--- a/Data/mappings/exiobase/EXIO_3_8_IW_concordance.xlsx
+++ b/Data/mappings/exiobase/EXIO_3_8_IW_concordance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11max\PycharmProjects\IW_Reborn\Data\mappings\exiobase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D3F5E2-363A-4B6A-AA6E-22F111021766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEC1FD8-A3C9-494E-9228-49214C0B99A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F6C5F89E-E828-4CC7-9B1D-CAD80207A1E7}</author>
+  </authors>
+  <commentList>
+    <comment ref="B520" authorId="0" shapeId="0" xr:uid="{F6C5F89E-E828-4CC7-9B1D-CAD80207A1E7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Aggregated CF value should be ~0.17 (considering extraction volumes of non-metallic minerals). Perlite is the closest of this value.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1178">
   <si>
     <t>Taxes less subsidies on products purchased: Total</t>
   </si>
@@ -3501,6 +3519,78 @@
   </si>
   <si>
     <t>Nitrogen, organic bound</t>
+  </si>
+  <si>
+    <t>Wood, soft, standing</t>
+  </si>
+  <si>
+    <t>Wood, hard, standing</t>
+  </si>
+  <si>
+    <t>Coal, brown</t>
+  </si>
+  <si>
+    <t>Bauxite</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Nickel</t>
+  </si>
+  <si>
+    <t>Magnesium</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Zinc</t>
+  </si>
+  <si>
+    <t>Granite</t>
+  </si>
+  <si>
+    <t>Phosphate ore</t>
+  </si>
+  <si>
+    <t>Clay, unspecified</t>
+  </si>
+  <si>
+    <t>Gravel</t>
+  </si>
+  <si>
+    <t>Limestone</t>
+  </si>
+  <si>
+    <t>Perlite</t>
+  </si>
+  <si>
+    <t>Salt, unspecified</t>
+  </si>
+  <si>
+    <t>Slate</t>
+  </si>
+  <si>
+    <t>Carbon monoxide, biogenic</t>
   </si>
 </sst>
 </file>
@@ -3585,6 +3675,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Maxime AGEZ" id="{2EF719DD-DD77-4200-87D4-5E53B038C482}" userId="457aefaf84304b8c" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3848,8 +3944,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B520" dT="2022-11-18T18:54:28.23" personId="{2EF719DD-DD77-4200-87D4-5E53B038C482}" id="{F6C5F89E-E828-4CC7-9B1D-CAD80207A1E7}">
+    <text>Aggregated CF value should be ~0.17 (considering extraction volumes of non-metallic minerals). Perlite is the closest of this value.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4433,7 +4537,7 @@
         <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>1122</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -4441,7 +4545,7 @@
         <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>1122</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -4449,7 +4553,7 @@
         <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>1122</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -7586,242 +7690,317 @@
         <v>475</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B494" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B495" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B498" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B499" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B501" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B503" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B504" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B505" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B506" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B507" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B508" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B509" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B510" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B511" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B512" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B513" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B514" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B515" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B516" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B517" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B518" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B519" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B520" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B521" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B522" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
         <v>523</v>
       </c>
@@ -11069,5 +11248,6 @@
   <autoFilter ref="A1:B1114" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>